--- a/QuickCross/QuickCrossApp/Templates/Analysis.xlsx
+++ b/QuickCross/QuickCrossApp/Templates/Analysis.xlsx
@@ -1483,14 +1483,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.33389823046312755"/>
-          <c:y val="3.4985422740524783E-2"/>
-        </c:manualLayout>
-      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1501,17 +1493,6 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.10338983050847457"/>
-          <c:y val="0.19533555503990957"/>
-          <c:w val="0.83898305084745761"/>
-          <c:h val="0.62682304975493375"/>
-        </c:manualLayout>
-      </c:layout>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -1590,9 +1571,6 @@
       </c:lineChart>
       <c:catAx>
         <c:axId val="95645056"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
@@ -1621,14 +1599,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout>
-            <c:manualLayout>
-              <c:xMode val="edge"/>
-              <c:yMode val="edge"/>
-              <c:x val="0.45932198797730928"/>
-              <c:y val="0.90087585990526686"/>
-            </c:manualLayout>
-          </c:layout>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -1637,10 +1607,8 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="in"/>
         <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:ln w="3175">
             <a:solidFill>
@@ -1671,14 +1639,10 @@
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:tickMarkSkip val="1"/>
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="153585536"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines>
@@ -1717,14 +1681,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout>
-            <c:manualLayout>
-              <c:xMode val="edge"/>
-              <c:yMode val="edge"/>
-              <c:x val="2.5423757514181695E-2"/>
-              <c:y val="0.44023384831998036"/>
-            </c:manualLayout>
-          </c:layout>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -1733,10 +1689,8 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="in"/>
         <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:ln w="3175">
             <a:solidFill>
